--- a/Zinc/5. Statistical data analysis/Sites with several typologies/Site_typology_sample_counts.xlsx
+++ b/Zinc/5. Statistical data analysis/Sites with several typologies/Site_typology_sample_counts.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Site</t>
   </si>
@@ -57,12 +57,6 @@
   </si>
   <si>
     <t xml:space="preserve">BSL3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.3</t>
   </si>
   <si>
     <t xml:space="preserve">Downtown</t>
@@ -577,7 +571,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -585,7 +579,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>2</v>
@@ -596,10 +590,10 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -695,10 +689,10 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -709,7 +703,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -717,7 +711,7 @@
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -728,10 +722,10 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -739,7 +733,7 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -750,10 +744,10 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -761,21 +755,21 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -783,21 +777,21 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -805,21 +799,21 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -827,21 +821,21 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -849,21 +843,21 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -871,21 +865,21 @@
         <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
@@ -893,21 +887,21 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -915,21 +909,21 @@
         <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -937,21 +931,21 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -959,21 +953,21 @@
         <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -984,18 +978,18 @@
         <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B50" t="s">
         <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -1003,7 +997,7 @@
         <v>28</v>
       </c>
       <c r="B51" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C51" t="n">
         <v>5</v>
@@ -1014,18 +1008,18 @@
         <v>28</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C53" t="n">
         <v>8</v>
@@ -1033,13 +1027,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1050,29 +1044,29 @@
         <v>5</v>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1083,7 +1077,7 @@
         <v>7</v>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
@@ -1091,21 +1085,21 @@
         <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
         <v>5</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -1113,75 +1107,9 @@
         <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>33</v>
-      </c>
-      <c r="B62" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>34</v>
-      </c>
-      <c r="B63" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>34</v>
-      </c>
-      <c r="B64" t="s">
-        <v>5</v>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>35</v>
-      </c>
-      <c r="B65" t="s">
-        <v>5</v>
-      </c>
-      <c r="C65" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>35</v>
-      </c>
-      <c r="B66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C66" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>35</v>
-      </c>
-      <c r="B67" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Zinc/5. Statistical data analysis/Sites with several typologies/Site_typology_sample_counts.xlsx
+++ b/Zinc/5. Statistical data analysis/Sites with several typologies/Site_typology_sample_counts.xlsx
@@ -546,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -557,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
